--- a/Result/profitability/2424.xlsx
+++ b/Result/profitability/2424.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.39625</v>
+        <v>-0.3425</v>
       </c>
       <c r="N2" t="n">
-        <v>4.867500000000001</v>
+        <v>17.01</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.34125</v>
+        <v>-0.35875</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2837500000000013</v>
+        <v>-1.829999999999998</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3225</v>
+        <v>-0.33875</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.671250000000001</v>
+        <v>-3.617499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.32</v>
+        <v>-0.31625</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.356250000000001</v>
+        <v>-3.171249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.26</v>
+        <v>-0.235</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.420000000000002</v>
+        <v>0.1337500000000009</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2375</v>
+        <v>-0.28125</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.873750000000001</v>
+        <v>-7.573749999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.27125</v>
+        <v>-0.24875</v>
       </c>
       <c r="N8" t="n">
-        <v>-13.91375</v>
+        <v>-9.891249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.28125</v>
       </c>
       <c r="N11" t="n">
-        <v>2.442499999999999</v>
+        <v>2.442500000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.235</v>
       </c>
       <c r="N12" t="n">
-        <v>3.228749999999999</v>
+        <v>3.228750000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.225</v>
       </c>
       <c r="N13" t="n">
-        <v>7.333749999999998</v>
+        <v>7.33375</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>50</v>
+      </c>
+      <c r="D75" t="n">
+        <v>35</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-48.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.548750000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3103448275862069</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-16.76041666666667</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.02999999999999997</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.06976744186046502</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.696969696969697</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
